--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/67.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/67.xlsx
@@ -426,13 +426,13 @@
         <v>-7.633178149949661</v>
       </c>
       <c r="E2">
-        <v>-11.54787802067491</v>
+        <v>-13.96537096220846</v>
       </c>
       <c r="F2">
-        <v>-3.175666699152818</v>
+        <v>-4.167499155016362</v>
       </c>
       <c r="G2">
-        <v>-3.179428182131159</v>
+        <v>-2.851594373080473</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.811351845213563</v>
       </c>
       <c r="E3">
-        <v>-13.50438942442044</v>
+        <v>-14.92303919554405</v>
       </c>
       <c r="F3">
-        <v>-3.494597261272059</v>
+        <v>-4.138724984912718</v>
       </c>
       <c r="G3">
-        <v>-2.555269640499933</v>
+        <v>-3.493722669732332</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.161970809074404</v>
       </c>
       <c r="E4">
-        <v>-14.23901359676744</v>
+        <v>-15.21925453365347</v>
       </c>
       <c r="F4">
-        <v>-3.114113202552995</v>
+        <v>-4.244152961001816</v>
       </c>
       <c r="G4">
-        <v>-0.6890832993262448</v>
+        <v>-2.607844815075772</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.775809908538935</v>
       </c>
       <c r="E5">
-        <v>-13.25782572769934</v>
+        <v>-15.38292013233099</v>
       </c>
       <c r="F5">
-        <v>-3.129981408521023</v>
+        <v>-4.245764963967664</v>
       </c>
       <c r="G5">
-        <v>-1.096325515860233</v>
+        <v>-2.562976558532899</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.601523947857224</v>
       </c>
       <c r="E6">
-        <v>-14.08937754594519</v>
+        <v>-15.46882930858507</v>
       </c>
       <c r="F6">
-        <v>-4.476647526475943</v>
+        <v>-4.064577818688134</v>
       </c>
       <c r="G6">
-        <v>-1.279928739974866</v>
+        <v>-1.933424218576432</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.611926055114882</v>
       </c>
       <c r="E7">
-        <v>-15.93853674336655</v>
+        <v>-16.4242298885373</v>
       </c>
       <c r="F7">
-        <v>-3.741473113226187</v>
+        <v>-4.236207260874164</v>
       </c>
       <c r="G7">
-        <v>-1.751089816333081</v>
+        <v>-2.152653663381397</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.748099990310985</v>
       </c>
       <c r="E8">
-        <v>-15.63990838947741</v>
+        <v>-16.91798857010087</v>
       </c>
       <c r="F8">
-        <v>-3.444512511363995</v>
+        <v>-3.826756850814007</v>
       </c>
       <c r="G8">
-        <v>-0.9661302938460045</v>
+        <v>-1.520892633500849</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.964104401003399</v>
       </c>
       <c r="E9">
-        <v>-14.83376176490554</v>
+        <v>-16.85577346445493</v>
       </c>
       <c r="F9">
-        <v>-3.529405259537694</v>
+        <v>-3.941441004261988</v>
       </c>
       <c r="G9">
-        <v>-1.197395271216002</v>
+        <v>-1.056112216923315</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.200623742412332</v>
       </c>
       <c r="E10">
-        <v>-15.78169487089573</v>
+        <v>-17.3665270867597</v>
       </c>
       <c r="F10">
-        <v>-3.331549705379032</v>
+        <v>-3.783673462194405</v>
       </c>
       <c r="G10">
-        <v>-0.1539563697411635</v>
+        <v>-1.75852260618398</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.4163679842892</v>
       </c>
       <c r="E11">
-        <v>-17.34892577716507</v>
+        <v>-17.76652286945394</v>
       </c>
       <c r="F11">
-        <v>-3.528724341532593</v>
+        <v>-3.921789644365375</v>
       </c>
       <c r="G11">
-        <v>0.3369889291285076</v>
+        <v>-1.656011719813917</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.572802030852723</v>
       </c>
       <c r="E12">
-        <v>-16.9571367400487</v>
+        <v>-18.6048195028913</v>
       </c>
       <c r="F12">
-        <v>-2.774951423355183</v>
+        <v>-3.387168777905199</v>
       </c>
       <c r="G12">
-        <v>-0.8153885118997145</v>
+        <v>-1.017240840706229</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.650466511005317</v>
       </c>
       <c r="E13">
-        <v>-18.89224249262606</v>
+        <v>-19.14182557398031</v>
       </c>
       <c r="F13">
-        <v>-3.006097406697551</v>
+        <v>-3.378775759380035</v>
       </c>
       <c r="G13">
-        <v>-0.3384629114843217</v>
+        <v>-1.1977190035453</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.648538843915176</v>
       </c>
       <c r="E14">
-        <v>-19.52703592435816</v>
+        <v>-19.00276359919107</v>
       </c>
       <c r="F14">
-        <v>-2.455850217550966</v>
+        <v>-2.736044663180496</v>
       </c>
       <c r="G14">
-        <v>0.03947630775901092</v>
+        <v>-0.893987588559771</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.580595525177318</v>
       </c>
       <c r="E15">
-        <v>-18.96341192188832</v>
+        <v>-19.56512917862948</v>
       </c>
       <c r="F15">
-        <v>-2.537839537977852</v>
+        <v>-2.832276932731117</v>
       </c>
       <c r="G15">
-        <v>-0.3094993109905109</v>
+        <v>-0.8699321878972532</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.476868398675035</v>
       </c>
       <c r="E16">
-        <v>-18.23502587295122</v>
+        <v>-19.87569801507751</v>
       </c>
       <c r="F16">
-        <v>-1.709807623976481</v>
+        <v>-2.514482062321115</v>
       </c>
       <c r="G16">
-        <v>0.9399064527664365</v>
+        <v>-0.6841907639624986</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.36858602267732</v>
       </c>
       <c r="E17">
-        <v>-20.61119851501405</v>
+        <v>-20.52147253755245</v>
       </c>
       <c r="F17">
-        <v>-1.72834234461412</v>
+        <v>-2.076618650344935</v>
       </c>
       <c r="G17">
-        <v>0.2300946025899653</v>
+        <v>-0.2373200552800019</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.294728855583063</v>
       </c>
       <c r="E18">
-        <v>-21.01236135009056</v>
+        <v>-20.74657659135816</v>
       </c>
       <c r="F18">
-        <v>-1.556022872381558</v>
+        <v>-2.007372934042716</v>
       </c>
       <c r="G18">
-        <v>0.7995293268468662</v>
+        <v>-0.8567113772878555</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.281422494618241</v>
       </c>
       <c r="E19">
-        <v>-21.30391678509353</v>
+        <v>-21.96633737855838</v>
       </c>
       <c r="F19">
-        <v>-1.641984214504868</v>
+        <v>-1.668657644875012</v>
       </c>
       <c r="G19">
-        <v>0.8473947181803372</v>
+        <v>-1.205344988495942</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.353483627749879</v>
       </c>
       <c r="E20">
-        <v>-22.08191709651703</v>
+        <v>-22.35229115376337</v>
       </c>
       <c r="F20">
-        <v>-0.8065119044915512</v>
+        <v>-1.238436750557061</v>
       </c>
       <c r="G20">
-        <v>0.8565401564830071</v>
+        <v>-0.9081874283908362</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.520972336426623</v>
       </c>
       <c r="E21">
-        <v>-23.04403341918151</v>
+        <v>-23.94331165450134</v>
       </c>
       <c r="F21">
-        <v>-0.633604291403002</v>
+        <v>-0.7477317819563011</v>
       </c>
       <c r="G21">
-        <v>1.199845237980631</v>
+        <v>-0.9276218111270835</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.783343812159308</v>
       </c>
       <c r="E22">
-        <v>-23.26141665313436</v>
+        <v>-23.54189132032268</v>
       </c>
       <c r="F22">
-        <v>-0.1449834951876856</v>
+        <v>-0.538655162959317</v>
       </c>
       <c r="G22">
-        <v>0.07630869245043716</v>
+        <v>-1.353423810959296</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.133027088679234</v>
       </c>
       <c r="E23">
-        <v>-24.45687700087301</v>
+        <v>-23.7727849507152</v>
       </c>
       <c r="F23">
-        <v>-0.005517902517555259</v>
+        <v>-0.3481248617436112</v>
       </c>
       <c r="G23">
-        <v>-0.6534022529994995</v>
+        <v>-1.462276195941173</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.548592708903747</v>
       </c>
       <c r="E24">
-        <v>-23.53809943838312</v>
+        <v>-23.9520873900307</v>
       </c>
       <c r="F24">
-        <v>0.382457082625024</v>
+        <v>-0.1951411414271957</v>
       </c>
       <c r="G24">
-        <v>-1.056733574136</v>
+        <v>-1.481958599413576</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.016486440065679</v>
       </c>
       <c r="E25">
-        <v>-23.7129164094678</v>
+        <v>-24.85344638422426</v>
       </c>
       <c r="F25">
-        <v>0.4038198495758205</v>
+        <v>0.4749981470287707</v>
       </c>
       <c r="G25">
-        <v>-0.6662183981972747</v>
+        <v>-2.108406764051209</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.512723778293001</v>
       </c>
       <c r="E26">
-        <v>-24.15493023113532</v>
+        <v>-24.53126932212334</v>
       </c>
       <c r="F26">
-        <v>0.475641788500746</v>
+        <v>0.9032790048893655</v>
       </c>
       <c r="G26">
-        <v>-1.324830936197423</v>
+        <v>-2.392142486213401</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.024804880034965</v>
       </c>
       <c r="E27">
-        <v>-24.70757314286231</v>
+        <v>-25.41743586929068</v>
       </c>
       <c r="F27">
-        <v>0.6119488162640018</v>
+        <v>0.5235089988715154</v>
       </c>
       <c r="G27">
-        <v>-1.748682709820074</v>
+        <v>-2.467023862575712</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.536292196003668</v>
       </c>
       <c r="E28">
-        <v>-25.49546640366156</v>
+        <v>-25.06767317757025</v>
       </c>
       <c r="F28">
-        <v>0.7050838200955558</v>
+        <v>0.634130838576167</v>
       </c>
       <c r="G28">
-        <v>-1.116950398130028</v>
+        <v>-2.787364834649904</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-10.03078091126451</v>
       </c>
       <c r="E29">
-        <v>-24.55234686959685</v>
+        <v>-24.97467446958468</v>
       </c>
       <c r="F29">
-        <v>0.6133355032962882</v>
+        <v>0.7000456895517293</v>
       </c>
       <c r="G29">
-        <v>-1.022292631490034</v>
+        <v>-2.734760941883562</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-10.49557991146913</v>
       </c>
       <c r="E30">
-        <v>-24.71114905781299</v>
+        <v>-24.44653135146286</v>
       </c>
       <c r="F30">
-        <v>1.731079804385356</v>
+        <v>0.4067613822231615</v>
       </c>
       <c r="G30">
-        <v>-0.5586165598745406</v>
+        <v>-2.987491461281693</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-10.90935081395648</v>
       </c>
       <c r="E31">
-        <v>-24.7871279057894</v>
+        <v>-24.27843427630175</v>
       </c>
       <c r="F31">
-        <v>0.3884718583367512</v>
+        <v>0.6819210107784761</v>
       </c>
       <c r="G31">
-        <v>-1.394509098589646</v>
+        <v>-2.90240468431272</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.25944559419661</v>
       </c>
       <c r="E32">
-        <v>-23.93408737214889</v>
+        <v>-24.80883674138428</v>
       </c>
       <c r="F32">
-        <v>0.2340633460875206</v>
+        <v>0.4442209845451579</v>
       </c>
       <c r="G32">
-        <v>-1.428205979027145</v>
+        <v>-3.28868784326925</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.52593894209852</v>
       </c>
       <c r="E33">
-        <v>-22.964358213126</v>
+        <v>-23.61539900756082</v>
       </c>
       <c r="F33">
-        <v>0.3492320944661386</v>
+        <v>0.5612941495828121</v>
       </c>
       <c r="G33">
-        <v>-2.066425991026108</v>
+        <v>-2.880563195063466</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.69626892893056</v>
       </c>
       <c r="E34">
-        <v>-21.94616107794236</v>
+        <v>-23.38767012419783</v>
       </c>
       <c r="F34">
-        <v>0.07501846148482108</v>
+        <v>0.4839196639569214</v>
       </c>
       <c r="G34">
-        <v>-0.72464686214639</v>
+        <v>-3.079261744403916</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.76066562333485</v>
       </c>
       <c r="E35">
-        <v>-21.98308727983141</v>
+        <v>-23.91291845402624</v>
       </c>
       <c r="F35">
-        <v>0.385022536471494</v>
+        <v>0.1753022760025348</v>
       </c>
       <c r="G35">
-        <v>-2.016850561985458</v>
+        <v>-3.120970999991541</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.70866923361231</v>
       </c>
       <c r="E36">
-        <v>-22.17376121175429</v>
+        <v>-23.16496247332655</v>
       </c>
       <c r="F36">
-        <v>0.3986582922889767</v>
+        <v>0.3459799240427477</v>
       </c>
       <c r="G36">
-        <v>-1.03131275405233</v>
+        <v>-2.483338405525579</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.54099921422781</v>
       </c>
       <c r="E37">
-        <v>-21.75848161138468</v>
+        <v>-22.56902233353822</v>
       </c>
       <c r="F37">
-        <v>-0.7835470749837405</v>
+        <v>-0.05936923900614832</v>
       </c>
       <c r="G37">
-        <v>-0.9401847140995206</v>
+        <v>-2.625971214771872</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.25730392941408</v>
       </c>
       <c r="E38">
-        <v>-20.35210042651462</v>
+        <v>-21.87781583238098</v>
       </c>
       <c r="F38">
-        <v>0.159878074962408</v>
+        <v>-0.5131381334834811</v>
       </c>
       <c r="G38">
-        <v>-0.05749196784411875</v>
+        <v>-2.511482232217781</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.86617830942079</v>
       </c>
       <c r="E39">
-        <v>-20.63851003268612</v>
+        <v>-21.07127880594458</v>
       </c>
       <c r="F39">
-        <v>0.4332765944193709</v>
+        <v>-0.6515873193503765</v>
       </c>
       <c r="G39">
-        <v>-0.428256860951072</v>
+        <v>-2.08521551984835</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-10.38280271865522</v>
       </c>
       <c r="E40">
-        <v>-20.84330903632474</v>
+        <v>-21.15908599977411</v>
       </c>
       <c r="F40">
-        <v>-0.03554373576682894</v>
+        <v>-0.3301277515503891</v>
       </c>
       <c r="G40">
-        <v>-0.7779164947834655</v>
+        <v>-1.553782793859694</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.824077870964036</v>
       </c>
       <c r="E41">
-        <v>-20.83069988674256</v>
+        <v>-20.20918011840462</v>
       </c>
       <c r="F41">
-        <v>-0.6940162977217671</v>
+        <v>-0.7450851481043567</v>
       </c>
       <c r="G41">
-        <v>-0.1036368784920461</v>
+        <v>-1.754554274405488</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.220422385832826</v>
       </c>
       <c r="E42">
-        <v>-17.93993605511083</v>
+        <v>-20.81597259938472</v>
       </c>
       <c r="F42">
-        <v>-0.3227718490135295</v>
+        <v>-1.091358461455203</v>
       </c>
       <c r="G42">
-        <v>0.03257349906010739</v>
+        <v>-1.624831597162251</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.595396446825978</v>
       </c>
       <c r="E43">
-        <v>-19.41273124227623</v>
+        <v>-19.29057699079037</v>
       </c>
       <c r="F43">
-        <v>-1.01687414969768</v>
+        <v>-1.188668436996867</v>
       </c>
       <c r="G43">
-        <v>0.3901358567698008</v>
+        <v>-1.081209304677687</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.982003759292411</v>
       </c>
       <c r="E44">
-        <v>-18.97169342527003</v>
+        <v>-19.52556984076049</v>
       </c>
       <c r="F44">
-        <v>-0.1779450625124807</v>
+        <v>-1.583016052569183</v>
       </c>
       <c r="G44">
-        <v>0.9986012126638454</v>
+        <v>-0.685908633903451</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.406464917860696</v>
       </c>
       <c r="E45">
-        <v>-17.19569719854685</v>
+        <v>-19.56124177282944</v>
       </c>
       <c r="F45">
-        <v>-1.007224497822469</v>
+        <v>-1.516907363621365</v>
       </c>
       <c r="G45">
-        <v>0.7225671870454377</v>
+        <v>-0.5784164468535438</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.89246241017262</v>
       </c>
       <c r="E46">
-        <v>-18.25769410036213</v>
+        <v>-19.16497972711623</v>
       </c>
       <c r="F46">
-        <v>-0.7158098157220193</v>
+        <v>-1.277552259317254</v>
       </c>
       <c r="G46">
-        <v>0.3848229915268853</v>
+        <v>-0.5539642130131768</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.463112292705048</v>
       </c>
       <c r="E47">
-        <v>-15.96645462989205</v>
+        <v>-18.29702085839693</v>
       </c>
       <c r="F47">
-        <v>-0.6188320155088785</v>
+        <v>-1.704302294217475</v>
       </c>
       <c r="G47">
-        <v>1.463177991163272</v>
+        <v>-0.8891759862783493</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.128849900613056</v>
       </c>
       <c r="E48">
-        <v>-16.80262066591978</v>
+        <v>-18.34330424540082</v>
       </c>
       <c r="F48">
-        <v>-1.242087365701198</v>
+        <v>-1.676848541753894</v>
       </c>
       <c r="G48">
-        <v>0.589280843435331</v>
+        <v>-0.7813287379640506</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.902242296547342</v>
       </c>
       <c r="E49">
-        <v>-17.10222917768159</v>
+        <v>-18.0907806904286</v>
       </c>
       <c r="F49">
-        <v>-1.041451810538741</v>
+        <v>-1.751896143345321</v>
       </c>
       <c r="G49">
-        <v>0.4517755365659855</v>
+        <v>-0.2862401874282826</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.779229608200224</v>
       </c>
       <c r="E50">
-        <v>-16.7888070850534</v>
+        <v>-17.37276936338091</v>
       </c>
       <c r="F50">
-        <v>-1.751241733097109</v>
+        <v>-1.960866731314746</v>
       </c>
       <c r="G50">
-        <v>0.04739991759303974</v>
+        <v>-0.7040298121103684</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.75810670818843</v>
       </c>
       <c r="E51">
-        <v>-15.28243318432676</v>
+        <v>-17.54227853039247</v>
       </c>
       <c r="F51">
-        <v>-0.9488229391902979</v>
+        <v>-2.074223011816039</v>
       </c>
       <c r="G51">
-        <v>0.5825712298361699</v>
+        <v>-0.6785567771348761</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.825573138084126</v>
       </c>
       <c r="E52">
-        <v>-15.49018927442866</v>
+        <v>-16.90335265339217</v>
       </c>
       <c r="F52">
-        <v>-1.279012671048389</v>
+        <v>-2.317905507432375</v>
       </c>
       <c r="G52">
-        <v>1.707632450207574</v>
+        <v>0.04064069984664744</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.96720022789905</v>
       </c>
       <c r="E53">
-        <v>-15.09955483006059</v>
+        <v>-16.22015769688052</v>
       </c>
       <c r="F53">
-        <v>-0.7623806311074075</v>
+        <v>-2.139465228460528</v>
       </c>
       <c r="G53">
-        <v>0.5684105511739715</v>
+        <v>-0.3226000273487173</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.166721034139268</v>
       </c>
       <c r="E54">
-        <v>-15.73350515989374</v>
+        <v>-16.99707402014825</v>
       </c>
       <c r="F54">
-        <v>-1.051662267145648</v>
+        <v>-2.350788379853904</v>
       </c>
       <c r="G54">
-        <v>0.7029291662310836</v>
+        <v>-1.110582792072303</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.406371817942246</v>
       </c>
       <c r="E55">
-        <v>-14.13725991930914</v>
+        <v>-16.39280253844232</v>
       </c>
       <c r="F55">
-        <v>-1.501851786075484</v>
+        <v>-2.444763348231897</v>
       </c>
       <c r="G55">
-        <v>-0.1903370956183272</v>
+        <v>-0.4869829497835743</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.673368235786713</v>
       </c>
       <c r="E56">
-        <v>-13.70427933227311</v>
+        <v>-16.13142018371424</v>
       </c>
       <c r="F56">
-        <v>-1.416329478675658</v>
+        <v>-2.813405066560539</v>
       </c>
       <c r="G56">
-        <v>0.6828473188362402</v>
+        <v>-0.4638961353643595</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.951357908495136</v>
       </c>
       <c r="E57">
-        <v>-14.90669215576952</v>
+        <v>-15.66526374461548</v>
       </c>
       <c r="F57">
-        <v>-1.560174649804389</v>
+        <v>-2.859619683962723</v>
       </c>
       <c r="G57">
-        <v>-0.5893136947768506</v>
+        <v>-0.9745003410051136</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.234153158064236</v>
       </c>
       <c r="E58">
-        <v>-13.66072875832096</v>
+        <v>-15.76557210453274</v>
       </c>
       <c r="F58">
-        <v>-1.773183528862462</v>
+        <v>-2.427040427649002</v>
       </c>
       <c r="G58">
-        <v>0.3778079208105639</v>
+        <v>-0.7106767678393429</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.510137054810083</v>
       </c>
       <c r="E59">
-        <v>-13.65761384982734</v>
+        <v>-15.23585907253013</v>
       </c>
       <c r="F59">
-        <v>-1.977093620368186</v>
+        <v>-2.988852454106071</v>
       </c>
       <c r="G59">
-        <v>-0.6980799251872212</v>
+        <v>-0.3824696223121272</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.776652044674995</v>
       </c>
       <c r="E60">
-        <v>-13.11833181893233</v>
+        <v>-15.5521718002404</v>
       </c>
       <c r="F60">
-        <v>-1.962477077545788</v>
+        <v>-2.794067657909587</v>
       </c>
       <c r="G60">
-        <v>-0.4373448628727374</v>
+        <v>-0.7241717066308074</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.028450621895571</v>
       </c>
       <c r="E61">
-        <v>-13.4907502784297</v>
+        <v>-15.79585732151339</v>
       </c>
       <c r="F61">
-        <v>-2.398379743879541</v>
+        <v>-2.920794616659466</v>
       </c>
       <c r="G61">
-        <v>-0.9362111608318462</v>
+        <v>-1.338265827863292</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.264180535077541</v>
       </c>
       <c r="E62">
-        <v>-14.34466713965975</v>
+        <v>-14.77155911889358</v>
       </c>
       <c r="F62">
-        <v>-2.418112283781629</v>
+        <v>-3.16610071238529</v>
       </c>
       <c r="G62">
-        <v>-0.4952381241806745</v>
+        <v>-1.029931670163631</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.484295760527836</v>
       </c>
       <c r="E63">
-        <v>-12.16596308324722</v>
+        <v>-14.36684944134566</v>
       </c>
       <c r="F63">
-        <v>-2.255318208313859</v>
+        <v>-3.262824203805771</v>
       </c>
       <c r="G63">
-        <v>-1.114086411313577</v>
+        <v>-1.24241756168975</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.685048538683777</v>
       </c>
       <c r="E64">
-        <v>-12.54785501777653</v>
+        <v>-14.55598668507835</v>
       </c>
       <c r="F64">
-        <v>-2.352535406706409</v>
+        <v>-3.240706794151024</v>
       </c>
       <c r="G64">
-        <v>-1.904350966809795</v>
+        <v>-1.432297015801419</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.872322310330309</v>
       </c>
       <c r="E65">
-        <v>-13.64423220293874</v>
+        <v>-14.35119183465106</v>
       </c>
       <c r="F65">
-        <v>-2.400753844855965</v>
+        <v>-3.56845367053826</v>
       </c>
       <c r="G65">
-        <v>-0.9026474283684939</v>
+        <v>-1.280030559013919</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.044543825120735</v>
       </c>
       <c r="E66">
-        <v>-13.0015352100555</v>
+        <v>-15.93629400925114</v>
       </c>
       <c r="F66">
-        <v>-2.283785054111064</v>
+        <v>-3.263212708117684</v>
       </c>
       <c r="G66">
-        <v>-0.8962772115661775</v>
+        <v>-2.06544696180444</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.207919486189803</v>
       </c>
       <c r="E67">
-        <v>-13.05999996587511</v>
+        <v>-14.85351859117774</v>
       </c>
       <c r="F67">
-        <v>-3.263184543625989</v>
+        <v>-3.372511645080065</v>
       </c>
       <c r="G67">
-        <v>-0.5574652215098597</v>
+        <v>-1.519234810685492</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.364867385137162</v>
       </c>
       <c r="E68">
-        <v>-13.91278715362481</v>
+        <v>-14.1848100357671</v>
       </c>
       <c r="F68">
-        <v>-2.578467645615557</v>
+        <v>-3.700520285566585</v>
       </c>
       <c r="G68">
-        <v>-1.749097818210061</v>
+        <v>-2.258762155798014</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.515321094116723</v>
       </c>
       <c r="E69">
-        <v>-11.01085533674061</v>
+        <v>-14.91939267600085</v>
       </c>
       <c r="F69">
-        <v>-2.925132776747927</v>
+        <v>-3.642545336146856</v>
       </c>
       <c r="G69">
-        <v>-1.048321755063433</v>
+        <v>-1.661073953576085</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.66036180481141</v>
       </c>
       <c r="E70">
-        <v>-12.70661567387943</v>
+        <v>-14.697777319708</v>
       </c>
       <c r="F70">
-        <v>-2.814950800134163</v>
+        <v>-3.821813982521503</v>
       </c>
       <c r="G70">
-        <v>-1.81290441601687</v>
+        <v>-2.064011052279328</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-9.791593330433988</v>
       </c>
       <c r="E71">
-        <v>-13.28783683273256</v>
+        <v>-14.09451922156533</v>
       </c>
       <c r="F71">
-        <v>-3.122661125782484</v>
+        <v>-4.110790779355513</v>
       </c>
       <c r="G71">
-        <v>-0.7599963439100639</v>
+        <v>-1.701203708686088</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.906098265055236</v>
       </c>
       <c r="E72">
-        <v>-11.74895990017781</v>
+        <v>-14.33171327353761</v>
       </c>
       <c r="F72">
-        <v>-2.923191083555766</v>
+        <v>-3.805177051603677</v>
       </c>
       <c r="G72">
-        <v>-0.5732680585198684</v>
+        <v>-2.218473145267954</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.992585293603002</v>
       </c>
       <c r="E73">
-        <v>-14.08221740962119</v>
+        <v>-14.66019906364095</v>
       </c>
       <c r="F73">
-        <v>-3.807305955828872</v>
+        <v>-3.971547189149333</v>
       </c>
       <c r="G73">
-        <v>-1.347421709144327</v>
+        <v>-1.55381934428397</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.04236829552422</v>
       </c>
       <c r="E74">
-        <v>-12.51991221198308</v>
+        <v>-15.35892703050745</v>
       </c>
       <c r="F74">
-        <v>-3.088896870444376</v>
+        <v>-4.250662272053015</v>
       </c>
       <c r="G74">
-        <v>-1.014410793569462</v>
+        <v>-2.440151468499383</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.04942844270889</v>
       </c>
       <c r="E75">
-        <v>-11.13415172134079</v>
+        <v>-14.87088732093818</v>
       </c>
       <c r="F75">
-        <v>-3.694609884147611</v>
+        <v>-4.435150461432702</v>
       </c>
       <c r="G75">
-        <v>-1.159406326670712</v>
+        <v>-1.49284801510311</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.00484930508844</v>
       </c>
       <c r="E76">
-        <v>-13.74164992777392</v>
+        <v>-15.85361187819646</v>
       </c>
       <c r="F76">
-        <v>-3.574536372377017</v>
+        <v>-4.15294639648398</v>
       </c>
       <c r="G76">
-        <v>-0.7262864097496091</v>
+        <v>-1.680458732165102</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.910463992985669</v>
       </c>
       <c r="E77">
-        <v>-11.76037707810976</v>
+        <v>-16.61023145771975</v>
       </c>
       <c r="F77">
-        <v>-3.484654367336256</v>
+        <v>-4.304023215039151</v>
       </c>
       <c r="G77">
-        <v>-1.002028031973812</v>
+        <v>-1.463409259093716</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.765185510050816</v>
       </c>
       <c r="E78">
-        <v>-14.95170881331934</v>
+        <v>-16.63985631409975</v>
       </c>
       <c r="F78">
-        <v>-3.667924028266424</v>
+        <v>-4.340029032569235</v>
       </c>
       <c r="G78">
-        <v>-0.5098661261246822</v>
+        <v>-1.214396439993331</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.577752243124367</v>
       </c>
       <c r="E79">
-        <v>-15.48769734763376</v>
+        <v>-16.26278625791857</v>
       </c>
       <c r="F79">
-        <v>-3.241487116244461</v>
+        <v>-4.209842811545264</v>
       </c>
       <c r="G79">
-        <v>-0.3005261818308545</v>
+        <v>-1.236697420290621</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.356464377056335</v>
       </c>
       <c r="E80">
-        <v>-15.15904127586611</v>
+        <v>-17.41205458930247</v>
       </c>
       <c r="F80">
-        <v>-3.880805338744467</v>
+        <v>-4.179901471771076</v>
       </c>
       <c r="G80">
-        <v>0.07119946528562845</v>
+        <v>-1.353630059781994</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.109656185819127</v>
       </c>
       <c r="E81">
-        <v>-18.26847583696139</v>
+        <v>-18.32469785866559</v>
       </c>
       <c r="F81">
-        <v>-3.523435215665718</v>
+        <v>-4.706278425838591</v>
       </c>
       <c r="G81">
-        <v>0.2623816809482633</v>
+        <v>-0.5818286900341288</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.850640876651521</v>
       </c>
       <c r="E82">
-        <v>-18.0169448994958</v>
+        <v>-19.77207123931171</v>
       </c>
       <c r="F82">
-        <v>-3.90264358858447</v>
+        <v>-4.355745647302549</v>
       </c>
       <c r="G82">
-        <v>0.1426790414457191</v>
+        <v>-0.8706396996814449</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.583954532326535</v>
       </c>
       <c r="E83">
-        <v>-18.15412546955488</v>
+        <v>-20.67374587756597</v>
       </c>
       <c r="F83">
-        <v>-3.943323055001148</v>
+        <v>-4.463296729045023</v>
       </c>
       <c r="G83">
-        <v>0.9103658777179896</v>
+        <v>-0.36978923583309</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.322000296707332</v>
       </c>
       <c r="E84">
-        <v>-19.74983909908991</v>
+        <v>-20.79549726755332</v>
       </c>
       <c r="F84">
-        <v>-4.264018039688351</v>
+        <v>-4.244101602222843</v>
       </c>
       <c r="G84">
-        <v>0.7908303258692767</v>
+        <v>-0.5173798490579062</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.069719221735717</v>
       </c>
       <c r="E85">
-        <v>-19.49454950537535</v>
+        <v>-22.0565700478016</v>
       </c>
       <c r="F85">
-        <v>-3.910025998878219</v>
+        <v>-4.625228474046479</v>
       </c>
       <c r="G85">
-        <v>1.352135191469451</v>
+        <v>-0.4540196885761779</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.8385894472189</v>
       </c>
       <c r="E86">
-        <v>-22.42921278071052</v>
+        <v>-23.72059985041873</v>
       </c>
       <c r="F86">
-        <v>-4.486421433461574</v>
+        <v>-4.327400571513556</v>
       </c>
       <c r="G86">
-        <v>0.3934253949546035</v>
+        <v>-0.06862418278062579</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.637811831330063</v>
       </c>
       <c r="E87">
-        <v>-22.74528046895262</v>
+        <v>-25.17463498202988</v>
       </c>
       <c r="F87">
-        <v>-3.976639163574342</v>
+        <v>-4.039258769021568</v>
       </c>
       <c r="G87">
-        <v>0.9881895632344856</v>
+        <v>0.2758035188911767</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.478042156538363</v>
       </c>
       <c r="E88">
-        <v>-23.60443037645195</v>
+        <v>-25.30283215599336</v>
       </c>
       <c r="F88">
-        <v>-4.012241566179261</v>
+        <v>-4.320822505967925</v>
       </c>
       <c r="G88">
-        <v>1.195179837396311</v>
+        <v>-0.1360623263136731</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.373891760128189</v>
       </c>
       <c r="E89">
-        <v>-25.39897899816314</v>
+        <v>-27.70821848651503</v>
       </c>
       <c r="F89">
-        <v>-3.844691005084617</v>
+        <v>-4.230781454385827</v>
       </c>
       <c r="G89">
-        <v>1.118160261213878</v>
+        <v>-0.007595417218761625</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.333360166062049</v>
       </c>
       <c r="E90">
-        <v>-28.33716419670177</v>
+        <v>-28.50774904544645</v>
       </c>
       <c r="F90">
-        <v>-3.990719752687128</v>
+        <v>-4.230668796419047</v>
       </c>
       <c r="G90">
-        <v>1.015448347510299</v>
+        <v>-0.06307896126910117</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.372373255544518</v>
       </c>
       <c r="E91">
-        <v>-30.61599387173327</v>
+        <v>-31.37954308435203</v>
       </c>
       <c r="F91">
-        <v>-3.855158255586391</v>
+        <v>-4.110194354825498</v>
       </c>
       <c r="G91">
-        <v>0.8116849536630897</v>
+        <v>-0.1764949277962445</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-7.495002872837291</v>
       </c>
       <c r="E92">
-        <v>-30.19269857350674</v>
+        <v>-32.29801746241522</v>
       </c>
       <c r="F92">
-        <v>-3.689860853827361</v>
+        <v>-3.65595660439818</v>
       </c>
       <c r="G92">
-        <v>1.122332231070477</v>
+        <v>-0.6806636480199045</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.712109334487287</v>
       </c>
       <c r="E93">
-        <v>-32.62271760039597</v>
+        <v>-34.22696400259786</v>
       </c>
       <c r="F93">
-        <v>-3.421925417391861</v>
+        <v>-3.974602208130858</v>
       </c>
       <c r="G93">
-        <v>0.8379673194618271</v>
+        <v>-0.7997658162664926</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.020717706142502</v>
       </c>
       <c r="E94">
-        <v>-33.34562971680695</v>
+        <v>-35.97808041687965</v>
       </c>
       <c r="F94">
-        <v>-3.864059063329472</v>
+        <v>-3.909262244132838</v>
       </c>
       <c r="G94">
-        <v>0.8454758209058689</v>
+        <v>-0.547379915154389</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.420277108883004</v>
       </c>
       <c r="E95">
-        <v>-35.8818214380041</v>
+        <v>-38.55992008374799</v>
       </c>
       <c r="F95">
-        <v>-3.253729558090436</v>
+        <v>-3.767947735419659</v>
       </c>
       <c r="G95">
-        <v>-0.3906281991593562</v>
+        <v>-1.588745885423883</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.908914083603673</v>
       </c>
       <c r="E96">
-        <v>-39.02716466421385</v>
+        <v>-39.36375129300627</v>
       </c>
       <c r="F96">
-        <v>-3.386845714618107</v>
+        <v>-3.724805532714458</v>
       </c>
       <c r="G96">
-        <v>-0.8772762124320549</v>
+        <v>-1.633133764961991</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.464747775234121</v>
       </c>
       <c r="E97">
-        <v>-40.83711339351751</v>
+        <v>-42.71873409065373</v>
       </c>
       <c r="F97">
-        <v>-3.622171639875003</v>
+        <v>-3.799123342624019</v>
       </c>
       <c r="G97">
-        <v>-0.07048042218490734</v>
+        <v>-1.854543181500536</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.09106307580202</v>
       </c>
       <c r="E98">
-        <v>-41.78758826483849</v>
+        <v>-44.05015604092763</v>
       </c>
       <c r="F98">
-        <v>-3.391966681902214</v>
+        <v>-3.588360995962338</v>
       </c>
       <c r="G98">
-        <v>-1.482258835041554</v>
+        <v>-2.531579744080171</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.7443081475545</v>
       </c>
       <c r="E99">
-        <v>-44.62820206972292</v>
+        <v>-45.40213015744244</v>
       </c>
       <c r="F99">
-        <v>-3.480810742587267</v>
+        <v>-3.442862403497619</v>
       </c>
       <c r="G99">
-        <v>-1.046525562784747</v>
+        <v>-2.153217584213078</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.44259242752006</v>
       </c>
       <c r="E100">
-        <v>-47.69317650358592</v>
+        <v>-48.05284771922456</v>
       </c>
       <c r="F100">
-        <v>-3.296414501989291</v>
+        <v>-3.454859648592364</v>
       </c>
       <c r="G100">
-        <v>-1.460339023454567</v>
+        <v>-3.022081216369353</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.11016152444983</v>
       </c>
       <c r="E101">
-        <v>-49.58058158579479</v>
+        <v>-50.2774032286632</v>
       </c>
       <c r="F101">
-        <v>-3.18420385360607</v>
+        <v>-3.316102310051627</v>
       </c>
       <c r="G101">
-        <v>-1.89153482161202</v>
+        <v>-3.678618212419566</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.81565984201859</v>
       </c>
       <c r="E102">
-        <v>-51.13400617931758</v>
+        <v>-51.50791771828623</v>
       </c>
       <c r="F102">
-        <v>-3.388856162304702</v>
+        <v>-3.579171916363083</v>
       </c>
       <c r="G102">
-        <v>-3.088830123330346</v>
+        <v>-3.617803527914173</v>
       </c>
     </row>
   </sheetData>
